--- a/data/trans_orig/IP07A04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A04-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17904</t>
+          <t>17821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13292</t>
+          <t>13627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26528</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11432</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22401</t>
+          <t>22366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19509</t>
+          <t>19469</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>33157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14116</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>13206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12669</t>
+          <t>12907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17859</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>17219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30795</t>
+          <t>30086</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>16873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11814</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21160</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16417</t>
+          <t>16199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>25073</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>19380</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>16523</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>29281</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>21043</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21685</t>
+          <t>22264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24874</t>
+          <t>25675</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34780</t>
+          <t>34013</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17556</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31204</t>
+          <t>31924</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>19614</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28948</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46373</t>
+          <t>46428</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>20713</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34994</t>
+          <t>34796</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>19376</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>34621</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44707</t>
+          <t>43983</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>63318</t>
+          <t>63556</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12958</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22569</t>
+          <t>22426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36997</t>
+          <t>37657</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21321</t>
+          <t>21538</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>36216</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45961</t>
+          <t>45984</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>13630</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>21909</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37446</t>
+          <t>37603</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23214</t>
+          <t>23151</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24614</t>
+          <t>24414</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39828</t>
+          <t>40057</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19692</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>26628</t>
+          <t>26648</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>22222</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>13175</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>18599</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14667</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17352</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>29878</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15284</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>27472</t>
+          <t>27594</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17508</t>
+          <t>17535</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>19645</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>50751</t>
+          <t>50393</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>72370</t>
+          <t>72742</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>27360</t>
+          <t>27352</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>45620</t>
+          <t>45408</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>80973</t>
+          <t>82606</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>111638</t>
+          <t>111491</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>61180</t>
+          <t>60880</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>84383</t>
+          <t>84120</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>49043</t>
+          <t>49091</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>70458</t>
+          <t>71758</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>115448</t>
+          <t>115797</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>147854</t>
+          <t>148740</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>75548</t>
+          <t>76290</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>102114</t>
+          <t>102149</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>76970</t>
+          <t>78783</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>102736</t>
+          <t>103837</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>162225</t>
+          <t>160541</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>197139</t>
+          <t>196745</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>23683</t>
+          <t>23967</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>41646</t>
+          <t>40661</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>52596</t>
+          <t>52208</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>75532</t>
+          <t>75253</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>80071</t>
+          <t>81890</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>111065</t>
+          <t>109501</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>32755</t>
+          <t>32514</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>53258</t>
+          <t>51345</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>64689</t>
+          <t>65504</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>89009</t>
+          <t>89606</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>102743</t>
+          <t>103456</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>134436</t>
+          <t>133342</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14143</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>20320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22671</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>15521</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>28454</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10620</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14683</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10620</t>
+          <t>10556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>21919</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>14274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27437</t>
+          <t>27016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>18318</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22692</t>
+          <t>22617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8997</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>19210</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>15586</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27975</t>
+          <t>28536</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23115</t>
+          <t>22521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30919</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10674</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21982</t>
+          <t>22269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29298</t>
+          <t>30066</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47539</t>
+          <t>48407</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24498</t>
+          <t>23633</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10975</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22585</t>
+          <t>23326</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25413</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42423</t>
+          <t>42734</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>11918</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23962</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21412</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35633</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36307</t>
+          <t>35504</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56224</t>
+          <t>55081</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15228</t>
+          <t>15597</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20916</t>
+          <t>21100</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>17744</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>32586</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25954</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>35397</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56149</t>
+          <t>56040</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>22489</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15935</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33923</t>
+          <t>34389</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>22324</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>20594</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35527</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29296</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12733</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>25023</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32745</t>
+          <t>32728</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>50359</t>
+          <t>50891</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16190</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>18110</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>30609</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18800</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25148</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>40075</t>
+          <t>40475</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>16802</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>26293</t>
+          <t>26424</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>12560</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>8878</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>63886</t>
+          <t>62250</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>87644</t>
+          <t>87465</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>43669</t>
+          <t>45368</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>66728</t>
+          <t>66958</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>115037</t>
+          <t>115001</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>149568</t>
+          <t>147486</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>52291</t>
+          <t>51687</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>75729</t>
+          <t>75843</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>43383</t>
+          <t>44326</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>65501</t>
+          <t>67182</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>102556</t>
+          <t>103732</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>133886</t>
+          <t>135656</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>67745</t>
+          <t>70112</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>93411</t>
+          <t>94505</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>64130</t>
+          <t>65005</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>90079</t>
+          <t>89562</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>139282</t>
+          <t>141009</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>175156</t>
+          <t>175103</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>25330</t>
+          <t>25880</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>43381</t>
+          <t>44661</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>33377</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>53244</t>
+          <t>53778</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>64335</t>
+          <t>63730</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>91477</t>
+          <t>91279</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>44011</t>
+          <t>42969</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>65608</t>
+          <t>64894</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>69211</t>
+          <t>69714</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>93334</t>
+          <t>95638</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>118800</t>
+          <t>119501</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>152438</t>
+          <t>153141</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2016 (tasa de respuesta: 98,82%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2016 (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>15856</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9621</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12322</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>16825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25666</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,8%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>14871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30541</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26340</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>22715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17745</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35987</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21932</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12690</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24924</t>
+          <t>23974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16755</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>23062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>20279</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>19903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28767</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25306</t>
+          <t>25441</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25474</t>
+          <t>25506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40481</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61491</t>
+          <t>62323</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28106</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10139</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28334</t>
+          <t>27428</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>47334</t>
+          <t>46610</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>24996</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27445</t>
+          <t>27435</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29387</t>
+          <t>28676</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48689</t>
+          <t>47645</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10057</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15051</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29796</t>
+          <t>29321</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>29170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46954</t>
+          <t>47884</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20724</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>35596</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35586</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45692</t>
+          <t>44977</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66095</t>
+          <t>67058</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>24313</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20991</t>
+          <t>20839</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>24577</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>41282</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22767</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>21895</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>24352</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>40068</t>
+          <t>41088</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>22428</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33147</t>
+          <t>32734</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>20250</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23497</t>
+          <t>23375</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23169</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>40047</t>
+          <t>39151</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11043</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24562</t>
+          <t>24365</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>23092</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>40164</t>
+          <t>40962</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>22276</t>
+          <t>22223</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>23291</t>
+          <t>23832</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>11179</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>16694</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>68932</t>
+          <t>65866</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>94743</t>
+          <t>92911</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>53005</t>
+          <t>52956</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>78079</t>
+          <t>78646</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>127563</t>
+          <t>127402</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>163575</t>
+          <t>163022</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>59247</t>
+          <t>59027</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>83791</t>
+          <t>83388</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>49203</t>
+          <t>49213</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>73034</t>
+          <t>72507</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>114399</t>
+          <t>115390</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>148086</t>
+          <t>149576</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>60745</t>
+          <t>60331</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>85089</t>
+          <t>86369</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>49220</t>
+          <t>48764</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>72493</t>
+          <t>73265</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>113901</t>
+          <t>115246</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>149413</t>
+          <t>149636</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>36845</t>
+          <t>37126</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>56755</t>
+          <t>57831</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>59568</t>
+          <t>59031</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>85548</t>
+          <t>84919</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>101018</t>
+          <t>101674</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>134233</t>
+          <t>134349</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>56166</t>
+          <t>56703</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>79678</t>
+          <t>81677</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>73878</t>
+          <t>74262</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>101529</t>
+          <t>102578</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>137785</t>
+          <t>138176</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>174885</t>
+          <t>176996</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
